--- a/hourly datasets/cap_gen_year-2final.xlsx
+++ b/hourly datasets/cap_gen_year-2final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1103252621312025</v>
+        <v>0.1077094442932192</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07044001546058171</v>
+        <v>0.06842575684158253</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1807652775917842</v>
+        <v>0.1761352011348017</v>
       </c>
     </row>
     <row r="4">
@@ -513,15 +513,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07385558919791943</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>0.07708527020396518</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.008107908985142982</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13.77470337849799</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09325567500487046</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06118965461290317</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09298088579502747</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.184180851329122</v>
+        <v>0.1847947144971844</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +541,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09775034134038381</v>
+        <v>0.0988533077923323</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +549,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.2080756034715864</v>
+        <v>0.2065627520855515</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03325985873978371</v>
+        <v>0.03572180111864767</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004473998508572849</v>
+        <v>0.003958177924362488</v>
       </c>
       <c r="D6" t="n">
-        <v>3.424008379840878</v>
+        <v>3.991889999256496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04199102364994203</v>
+        <v>0.03921567554991281</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02447910647282289</v>
+        <v>0.02796168239894187</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04204061100674416</v>
+        <v>0.04348191983835401</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1435851208709862</v>
+        <v>0.1434312454118669</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0215173363589086</v>
+        <v>0.02427692708415669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003392600486410443</v>
+        <v>0.002511964064889335</v>
       </c>
       <c r="D7" t="n">
-        <v>2.282667270780109</v>
+        <v>3.152155281255804</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01055812936102949</v>
+        <v>0.006320192417996793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0148560266571679</v>
+        <v>0.01935224443060547</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02817864606064947</v>
+        <v>0.02920160973770751</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1318425984901112</v>
+        <v>0.1319863713773759</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01772736247832942</v>
+        <v>0.02115331755335478</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002272195427779487</v>
+        <v>0.001732949467800252</v>
       </c>
       <c r="D8" t="n">
-        <v>1.406905289337423</v>
+        <v>2.232308201978884</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007850944809638025</v>
+        <v>0.005105568917197244</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01326402396897121</v>
+        <v>0.01775542771892764</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02219070098768769</v>
+        <v>0.02455120738778213</v>
       </c>
       <c r="H8" t="n">
-        <v>0.128052624609532</v>
+        <v>0.128862761846574</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.004661347441169542</v>
+        <v>0.00120909159938833</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001404839124170956</v>
+        <v>0.0008794419344065201</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.185296486376566</v>
+        <v>0.05619752297674723</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01305524404181429</v>
+        <v>0.005910057154000305</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.007424153017588027</v>
+        <v>-0.0005152746843245111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.001898541864751114</v>
+        <v>0.00293345788310121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.105663914690033</v>
+        <v>0.1089185358926075</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.00368091932506366</v>
+        <v>0.001990523116050212</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00136732187542834</v>
+        <v>0.000972178593526292</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.074489543303176</v>
+        <v>0.1012087940975867</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01162710166436559</v>
+        <v>0.01829423404476438</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.006365935177336264</v>
+        <v>8.419465236955246e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0009959034727909342</v>
+        <v>0.00389685157973085</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1066443428061389</v>
+        <v>0.1096999674092694</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02280907856625295</v>
+        <v>0.02360505802679245</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1331343406974555</v>
+        <v>0.1313145023200116</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03855261159719801</v>
+        <v>0.03676091623685585</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1488778737284006</v>
+        <v>0.144470360530075</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04638141113000906</v>
+        <v>0.04496501150248283</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1567066732612116</v>
+        <v>0.152674455795702</v>
       </c>
     </row>
     <row r="14">
@@ -743,25 +753,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05111241853132317</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.007902941855811025</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.4731162499843</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.05140022376806589</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.03561372598762831</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.06661111107501799</v>
-      </c>
+        <v>0.05095407835568483</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1614376806625257</v>
+        <v>0.158663522648904</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05428383737247126</v>
+        <v>0.05414023046534468</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1646090995036738</v>
+        <v>0.1618496747585639</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05753670300054921</v>
+        <v>0.05828964246614888</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +797,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1678619651317518</v>
+        <v>0.1659990867593681</v>
       </c>
     </row>
     <row r="17">
@@ -807,25 +807,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06111087613414442</v>
+        <v>0.06132373369515383</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007994937199944796</v>
+        <v>0.007165489101171619</v>
       </c>
       <c r="D17" t="n">
-        <v>12.6138069044918</v>
+        <v>13.17881260737152</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03049948613231279</v>
+        <v>0.02822726811040783</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04541438353591733</v>
+        <v>0.04727234119213755</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07680736873237144</v>
+        <v>0.07537512619817001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.171436138265347</v>
+        <v>0.169033177988373</v>
       </c>
     </row>
     <row r="18">
@@ -835,22 +835,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1103252621312025</v>
+        <v>-0.1077094442932192</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01079776571032865</v>
+        <v>0.01025468318786665</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.82924910047596</v>
+        <v>-18.91030579831649</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02540323914022031</v>
+        <v>0.02326899608014034</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.131503506623016</v>
+        <v>-0.1278170907617711</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08914701763938887</v>
+        <v>-0.08760179782466707</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -863,25 +863,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06053595480278799</v>
+        <v>0.06229219689779635</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007702350448359535</v>
+        <v>0.007142759731470784</v>
       </c>
       <c r="D19" t="n">
-        <v>13.22787741156001</v>
+        <v>13.72284339654593</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03246888672319957</v>
+        <v>0.03021736989308508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04542557724254849</v>
+        <v>0.0482851403571159</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0756463323630274</v>
+        <v>0.07629925343847668</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1708612169339905</v>
+        <v>0.1700016411910155</v>
       </c>
     </row>
     <row r="20">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06410739842610239</v>
+        <v>0.06436907235316248</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007714953658747629</v>
+        <v>0.007031380026242377</v>
       </c>
       <c r="D20" t="n">
-        <v>13.16701210081154</v>
+        <v>13.71701747252535</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03671214015031309</v>
+        <v>0.03579700694645045</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04897271753641649</v>
+        <v>0.05058147836203385</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07924207931578836</v>
+        <v>0.07815666634429123</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1744326605573049</v>
+        <v>0.1720785166463817</v>
       </c>
     </row>
     <row r="21">
@@ -919,25 +919,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06493580266304178</v>
+        <v>0.06519747556900377</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008091728137715032</v>
+        <v>0.007411745855644417</v>
       </c>
       <c r="D21" t="n">
-        <v>12.96415324187086</v>
+        <v>13.61531364831183</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04375057291111382</v>
+        <v>0.04126225732423109</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04905205677625769</v>
+        <v>0.05066202383941683</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08081954854982591</v>
+        <v>0.07973292729859066</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1752610647942443</v>
+        <v>0.172906919862223</v>
       </c>
     </row>
     <row r="22">
@@ -947,25 +947,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06671571238734235</v>
+        <v>0.06731604031951505</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007376203888435457</v>
+        <v>0.007105548735165668</v>
       </c>
       <c r="D22" t="n">
-        <v>13.04364429162031</v>
+        <v>13.64095194695101</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05029477987668156</v>
+        <v>0.04700931048339061</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05224472843677717</v>
+        <v>0.05338107978152557</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0811866963379078</v>
+        <v>0.08125100085750465</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1770409745185449</v>
+        <v>0.1750254846127342</v>
       </c>
     </row>
     <row r="23">
@@ -975,25 +975,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.06604278817599865</v>
+        <v>0.0665347987728009</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007459508090423148</v>
+        <v>0.006993974176747915</v>
       </c>
       <c r="D23" t="n">
-        <v>12.99509838570167</v>
+        <v>13.68215998310413</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05522547490828641</v>
+        <v>0.05110026518766722</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05139904981892887</v>
+        <v>0.05282136034439745</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08068652653306826</v>
+        <v>0.0802482372012043</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1763680503072012</v>
+        <v>0.1742442430660201</v>
       </c>
     </row>
     <row r="24">
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06708940406478939</v>
+        <v>0.06744069215775372</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007363541803498185</v>
+        <v>0.00717542002129742</v>
       </c>
       <c r="D24" t="n">
-        <v>12.48003567790357</v>
+        <v>13.25170812209827</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0651694139027521</v>
+        <v>0.05918787570122735</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05264844764493008</v>
+        <v>0.05337305020210136</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08153036048464858</v>
+        <v>0.08150833411340624</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1774146661959919</v>
+        <v>0.1751501364509729</v>
       </c>
     </row>
     <row r="25">
@@ -1031,25 +1031,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06646527819494623</v>
+        <v>0.06729623593321729</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007271584233597669</v>
+        <v>0.006986023487894682</v>
       </c>
       <c r="D25" t="n">
-        <v>12.21144560552265</v>
+        <v>13.06566384224221</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05788372980018914</v>
+        <v>0.0545403017545434</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05220423129103739</v>
+        <v>0.05359991380088222</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08072632509885527</v>
+        <v>0.08099255806555243</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1767905403261488</v>
+        <v>0.1750056802264365</v>
       </c>
     </row>
     <row r="26">
@@ -1059,25 +1059,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.06632014545162199</v>
+        <v>0.06727531668036468</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007410540842542534</v>
+        <v>0.00723731218578267</v>
       </c>
       <c r="D26" t="n">
-        <v>11.90538710729939</v>
+        <v>12.77940887825625</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0685210476628932</v>
+        <v>0.06258090335738981</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05178683286311346</v>
+        <v>0.05308669184406119</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08085345804013061</v>
+        <v>0.08146394151666823</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1766454075828245</v>
+        <v>0.1749847609735839</v>
       </c>
     </row>
     <row r="27">
@@ -1087,25 +1087,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06772988741370799</v>
+        <v>0.06753568096677127</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007407180514326568</v>
+        <v>0.007091691893037833</v>
       </c>
       <c r="D27" t="n">
-        <v>11.81007766279104</v>
+        <v>12.86789152220478</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06806502373730966</v>
+        <v>0.06309913001125338</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05320223046072899</v>
+        <v>0.05363203200463118</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08225754436668717</v>
+        <v>0.08143932992891145</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1780551495449105</v>
+        <v>0.1752451252599905</v>
       </c>
     </row>
     <row r="28">
@@ -1115,25 +1115,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07052531004476637</v>
+        <v>0.06857484789535341</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007581069563438876</v>
+        <v>0.007144484320664998</v>
       </c>
       <c r="D28" t="n">
-        <v>11.72173514496359</v>
+        <v>12.74473018963246</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08494648414399333</v>
+        <v>0.07923962912024811</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05565808320331801</v>
+        <v>0.05456834686969358</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08539253688621451</v>
+        <v>0.08258134892101314</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1808505721759689</v>
+        <v>0.1762842921885726</v>
       </c>
     </row>
     <row r="29">
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.001817690184450246</v>
+        <v>0.002645233174263188</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001277505654093689</v>
+        <v>0.0009526075071748542</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8963953259688853</v>
+        <v>0.1344535272453581</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0173566803027261</v>
+        <v>0.03323853890526338</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.004325435997626286</v>
+        <v>0.0007772730872104813</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000690055628725829</v>
+        <v>0.004513193261315895</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1085075719467523</v>
+        <v>0.1103546774674824</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year-2final.xlsx
+++ b/hourly datasets/cap_gen_year-2final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2338240045637663</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1077094442932192</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1045271183569532</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06842575684158253</v>
+        <v>0.3323552830252729</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1761352011348017</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2030583968184597</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +524,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07708527020396518</v>
+        <v>0.3355464296453374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008107908985142982</v>
+        <v>0.008120778681944796</v>
       </c>
       <c r="D4" t="n">
-        <v>13.77470337849799</v>
+        <v>13.79656798703529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09325567500487046</v>
+        <v>0.09340369988583057</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06118965461290317</v>
+        <v>0.06128678104879667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09298088579502747</v>
+        <v>0.09312847450263863</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1847947144971844</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2062495434385242</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0988533077923323</v>
+        <v>0.3348037610060873</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -549,7 +563,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.2065627520855515</v>
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2055068747992741</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03572180111864767</v>
+        <v>0.3327088817449076</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003958177924362488</v>
+        <v>0.010351218751197</v>
       </c>
       <c r="D6" t="n">
-        <v>3.991889999256496</v>
+        <v>10.778986101154</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03921567554991281</v>
+        <v>0.05386945822133792</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02796168239894187</v>
+        <v>0.08801551796201655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04348191983835401</v>
+        <v>0.1286006459117809</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1434312454118669</v>
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2034119955380944</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02427692708415669</v>
+        <v>0.3040012672327754</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002511964064889335</v>
+        <v>0.009932974476007703</v>
       </c>
       <c r="D7" t="n">
-        <v>3.152155281255804</v>
+        <v>19.62195773072338</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006320192417996793</v>
+        <v>0.007334855844823958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01935224443060547</v>
+        <v>0.1524578226386034</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02920160973770751</v>
+        <v>0.1914019557830338</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1319863713773759</v>
+        <v>24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1747043810259622</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02115331755335478</v>
+        <v>0.3091338344564007</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001732949467800252</v>
+        <v>0.009600443604874392</v>
       </c>
       <c r="D8" t="n">
-        <v>2.232308201978884</v>
+        <v>19.6067966476833</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005105568917197244</v>
+        <v>0.006244342136126362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01775542771892764</v>
+        <v>0.1615553948927817</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02455120738778213</v>
+        <v>0.1991968998835475</v>
       </c>
       <c r="H8" t="n">
-        <v>0.128862761846574</v>
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1798369482495875</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00120909159938833</v>
+        <v>0.3050954252762341</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008794419344065201</v>
+        <v>0.01306935700533489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05619752297674723</v>
+        <v>-1.809852597734319</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005910057154000305</v>
+        <v>0.04424960708087241</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0005152746843245111</v>
+        <v>-0.04837278486883211</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00293345788310121</v>
+        <v>0.002866502692439816</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1089185358926075</v>
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1757985390694209</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001990523116050212</v>
+        <v>0.322946206111289</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000972178593526292</v>
+        <v>0.01315004588872014</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1012087940975867</v>
+        <v>-0.580969035155477</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01829423404476438</v>
+        <v>0.4240386728316226</v>
       </c>
       <c r="F10" t="n">
-        <v>8.419465236955246e-05</v>
+        <v>-0.0323316730303103</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00389685157973085</v>
+        <v>0.01922438819260467</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1096999674092694</v>
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1936493199044759</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02360505802679245</v>
+        <v>0.2680334698801287</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1313145023200116</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1387365836733156</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03676091623685585</v>
+        <v>0.2873521260259181</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.144470360530075</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1580552398191049</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04496501150248283</v>
+        <v>0.2984490172973073</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.152674455795702</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1691521310904942</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05095407835568483</v>
+        <v>0.3058867414587928</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.158663522648904</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1765898552519796</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05414023046534468</v>
+        <v>0.3111400064564085</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1618496747585639</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1818431202495954</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05828964246614888</v>
+        <v>0.315231452529359</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +844,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1659990867593681</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1859345663225459</v>
       </c>
     </row>
     <row r="17">
@@ -807,25 +857,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06132373369515383</v>
+        <v>0.3174101940565202</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007165489101171619</v>
+        <v>0.007164265789918892</v>
       </c>
       <c r="D17" t="n">
-        <v>13.17881260737152</v>
+        <v>13.17664782154694</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02822726811040783</v>
+        <v>0.02822034936119891</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04727234119213755</v>
+        <v>0.04726312139932035</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07537512619817001</v>
+        <v>0.07536110858437502</v>
       </c>
       <c r="H17" t="n">
-        <v>0.169033177988373</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1881133078497071</v>
       </c>
     </row>
     <row r="18">
@@ -835,24 +888,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1077094442932192</v>
+        <v>0.1292968862068131</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01025468318786665</v>
+        <v>0.01021415560669979</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.91030579831649</v>
+        <v>-18.81729758053203</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02326899608014034</v>
+        <v>0.02319586708382795</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1278170907617711</v>
+        <v>-0.127242067035134</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08760179782466707</v>
+        <v>-0.08718568802120989</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -863,25 +919,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06229219689779635</v>
+        <v>0.3192878589114904</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007142759731470784</v>
+        <v>0.007140171665740826</v>
       </c>
       <c r="D19" t="n">
-        <v>13.72284339654593</v>
+        <v>13.71563481754218</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03021736989308508</v>
+        <v>0.03020803367243588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0482851403571159</v>
+        <v>0.04825703877133539</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07629925343847668</v>
+        <v>0.07626100224505328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1700016411910155</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1899909727046772</v>
       </c>
     </row>
     <row r="20">
@@ -891,25 +950,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06436907235316248</v>
+        <v>0.3219638213364003</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007031380026242377</v>
+        <v>0.007042540946918953</v>
       </c>
       <c r="D20" t="n">
-        <v>13.71701747252535</v>
+        <v>13.73879051613253</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03579700694645045</v>
+        <v>0.0358538275923972</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05058147836203385</v>
+        <v>0.05066176642292596</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07815666634429123</v>
+        <v>0.07828072454483773</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1720785166463817</v>
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1926669351295872</v>
       </c>
     </row>
     <row r="21">
@@ -919,25 +981,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06519747556900377</v>
+        <v>0.324552216359412</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007411745855644417</v>
+        <v>0.007423510531605757</v>
       </c>
       <c r="D21" t="n">
-        <v>13.61531364831183</v>
+        <v>13.63692525727741</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04126225732423109</v>
+        <v>0.04132775297077749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05066202383941683</v>
+        <v>0.05074243975027305</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07973292729859066</v>
+        <v>0.07985948750065192</v>
       </c>
       <c r="H21" t="n">
-        <v>0.172906919862223</v>
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1952553301525989</v>
       </c>
     </row>
     <row r="22">
@@ -947,25 +1012,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06731604031951505</v>
+        <v>0.3272724184869575</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007105548735165668</v>
+        <v>0.007116827383951645</v>
       </c>
       <c r="D22" t="n">
-        <v>13.64095194695101</v>
+        <v>13.66260425162871</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04700931048339061</v>
+        <v>0.04708392843653885</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05338107978152557</v>
+        <v>0.05346581165419466</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08125100085750465</v>
+        <v>0.08137997070013561</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1750254846127342</v>
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1979755322801443</v>
       </c>
     </row>
     <row r="23">
@@ -975,25 +1043,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0665347987728009</v>
+        <v>0.3279316465110841</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006993974176747915</v>
+        <v>0.007005075723060213</v>
       </c>
       <c r="D23" t="n">
-        <v>13.68215998310413</v>
+        <v>13.70387769736302</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05110026518766722</v>
+        <v>0.05118137671971114</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05282136034439745</v>
+        <v>0.05290520377351554</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0802482372012043</v>
+        <v>0.08037561535549194</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1742442430660201</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1986347603042709</v>
       </c>
     </row>
     <row r="24">
@@ -1003,25 +1074,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06744069215775372</v>
+        <v>0.3296211476093073</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00717542002129742</v>
+        <v>0.007186809576886781</v>
       </c>
       <c r="D24" t="n">
-        <v>13.25170812209827</v>
+        <v>13.27274257943494</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05918787570122735</v>
+        <v>0.05928182471027692</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05337305020210136</v>
+        <v>0.05345776932940628</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08150833411340624</v>
+        <v>0.08163771242152276</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1751501364509729</v>
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2003242614024942</v>
       </c>
     </row>
     <row r="25">
@@ -1031,25 +1105,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06729623593321729</v>
+        <v>0.3311995472354761</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006986023487894682</v>
+        <v>0.006997112414065944</v>
       </c>
       <c r="D25" t="n">
-        <v>13.06566384224221</v>
+        <v>13.08640299119815</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0545403017545434</v>
+        <v>0.05462687366209029</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05359991380088222</v>
+        <v>0.05368499302913759</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08099255806555243</v>
+        <v>0.08112111768152951</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1750056802264365</v>
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2019026610286629</v>
       </c>
     </row>
     <row r="26">
@@ -1059,25 +1136,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.06727531668036468</v>
+        <v>0.3323123676098321</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00723731218578267</v>
+        <v>0.00724879998290296</v>
       </c>
       <c r="D26" t="n">
-        <v>12.77940887825625</v>
+        <v>12.79969365425348</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06258090335738981</v>
+        <v>0.06268023812462375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05308669184406119</v>
+        <v>0.05317095643428985</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08146394151666823</v>
+        <v>0.08159324936034548</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1749847609735839</v>
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.203015481403019</v>
       </c>
     </row>
     <row r="27">
@@ -1087,25 +1167,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06753568096677127</v>
+        <v>0.3332589142185479</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007091691893037833</v>
+        <v>0.007102948546836305</v>
       </c>
       <c r="D27" t="n">
-        <v>12.86789152220478</v>
+        <v>12.8883167468432</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06309913001125338</v>
+        <v>0.06319928736047759</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05363203200463118</v>
+        <v>0.05371716221416235</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08143932992891145</v>
+        <v>0.08156859870657639</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1752451252599905</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2039620280117347</v>
       </c>
     </row>
     <row r="28">
@@ -1115,25 +1198,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.06857484789535341</v>
+        <v>0.333308812364238</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007144484320664998</v>
+        <v>0.007155824771967641</v>
       </c>
       <c r="D28" t="n">
-        <v>12.74473018963246</v>
+        <v>12.76495992009219</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07923962912024811</v>
+        <v>0.07936540630932787</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05456834686969358</v>
+        <v>0.05465496329329627</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08258134892101314</v>
+        <v>0.08271243042723697</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1762842921885726</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2040119261574249</v>
       </c>
     </row>
     <row r="29">
@@ -1143,25 +1229,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002645233174263188</v>
+        <v>0.3292718936788416</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0009526075071748542</v>
+        <v>0.01315117517451502</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1344535272453581</v>
+        <v>-0.1240425664134801</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03323853890526338</v>
+        <v>0.7345690357318566</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0007772730872104813</v>
+        <v>-0.02600828836337423</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004513193261315895</v>
+        <v>0.02555237866077416</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1103546774674824</v>
+        <v>55</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1999750074720285</v>
       </c>
     </row>
   </sheetData>
